--- a/Result/profitability/2390.xlsx
+++ b/Result/profitability/2390.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.05124999999999999</v>
+        <v>-0.04624999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>22.76125</v>
+        <v>22.01625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02</v>
+        <v>0.001250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>22.5575</v>
+        <v>21.5425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06</v>
+        <v>-0.05624999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>20.64375</v>
+        <v>19.9275</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.007499999999999998</v>
+        <v>-0.02625</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1127,7 +1127,7 @@
         <v>-0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01625</v>
+        <v>-0.0225</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1250,7 +1250,7 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02875</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1375,11 +1375,11 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05875</v>
+        <v>-0.06375</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>-0.13</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.02500000000000001</v>
+        <v>-0.025</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
@@ -1623,7 +1623,7 @@
         <v>-0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04375000000000001</v>
+        <v>-0.04375</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
@@ -9798,6 +9798,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>175</v>
+      </c>
+      <c r="D75" t="n">
+        <v>144</v>
+      </c>
+      <c r="E75" t="n">
+        <v>31</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-67</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-82</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-84</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.10125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.814814814814815</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.609999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2414980628497632</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.517241379310345</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.11010101010101</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
